--- a/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.036602236209996</v>
+        <v>2.036602236209995</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3595551986980526</v>
+        <v>0.3595551986980818</v>
       </c>
       <c r="D2" t="n">
-        <v>1.33188699630767</v>
+        <v>1.331886996307612</v>
       </c>
       <c r="E2" t="n">
-        <v>2.741317476112322</v>
+        <v>2.741317476112378</v>
       </c>
       <c r="F2" t="n">
-        <v>1.476888557167581e-08</v>
+        <v>1.476888557171562e-08</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.06313566390614948</v>
+        <v>-0.0631356639061495</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06889171256433488</v>
+        <v>0.06889171256433489</v>
       </c>
       <c r="D3" t="n">
         <v>-0.1981609393655314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07188961155323241</v>
+        <v>0.07188961155323242</v>
       </c>
       <c r="F3" t="n">
         <v>0.3594320324412411</v>
@@ -1517,16 +1517,16 @@
         <v>-0.1420900222427463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1674834691504836</v>
+        <v>0.1674834691504837</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4703515897835194</v>
+        <v>-0.4703515897835195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1861715452980268</v>
+        <v>0.1861715452980269</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3962250586520983</v>
+        <v>0.3962250586520981</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1542,16 +1542,16 @@
         <v>0.1123402147235629</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1386455160915384</v>
+        <v>0.1386455160915385</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1594000034338209</v>
+        <v>-0.1594000034338211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3840804328809467</v>
+        <v>0.384080432880947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4177853765636296</v>
+        <v>0.41778537656363</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.261615745957696</v>
+        <v>0.2616157459576963</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1491654091054351</v>
+        <v>0.1491654091054355</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03074308362813982</v>
+        <v>-0.03074308362814021</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5539745755435319</v>
+        <v>0.5539745755435328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07945392276127186</v>
+        <v>0.07945392276127221</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2268721888728757</v>
+        <v>0.2268721888728756</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1322971139673635</v>
+        <v>0.1322971139673637</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03242538976174775</v>
+        <v>-0.03242538976174825</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4861697675074991</v>
+        <v>0.4861697675074994</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08636928988307624</v>
+        <v>0.08636928988307689</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2700551131784785</v>
+        <v>0.2700551131784784</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1556352113937795</v>
+        <v>0.1556352113937797</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03498429587960727</v>
+        <v>-0.03498429587960766</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5750945222365642</v>
+        <v>0.5750945222365644</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08270891977837894</v>
+        <v>0.08270891977837933</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1642,16 +1642,16 @@
         <v>0.05428434711664003</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1256761579998879</v>
+        <v>0.1256761579998883</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1920363962785057</v>
+        <v>-0.1920363962785064</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3006050905117857</v>
+        <v>0.3006050905117864</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6657862511070213</v>
+        <v>0.6657862511070221</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2497052052682605</v>
+        <v>0.249705205268261</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1813103926938767</v>
+        <v>0.1813103926938773</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1056566344345521</v>
+        <v>-0.1056566344345526</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6050670449710731</v>
+        <v>0.6050670449710747</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1684426953271448</v>
+        <v>0.1684426953271453</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.05406182499411169</v>
+        <v>-0.05406182499411179</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2032970913516041</v>
+        <v>0.2032970913516045</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.452516802205005</v>
+        <v>-0.4525168022050058</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3443931522167817</v>
+        <v>0.3443931522167823</v>
       </c>
       <c r="F11" t="n">
         <v>0.7902967967088366</v>
@@ -1717,16 +1717,16 @@
         <v>0.1958077105120102</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1454915101622126</v>
+        <v>0.1454915101622135</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08935040946226977</v>
+        <v>-0.08935040946227149</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4809658304862902</v>
+        <v>0.4809658304862918</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1783554160232425</v>
+        <v>0.1783554160232452</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1742,16 +1742,16 @@
         <v>0.2559736583242179</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1734212677168902</v>
+        <v>0.1734212677168909</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.08392578055416561</v>
+        <v>-0.08392578055416705</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5958730972026014</v>
+        <v>0.595873097202603</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1399379060136729</v>
+        <v>0.1399379060136746</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1767,16 +1767,16 @@
         <v>0.2621085393999598</v>
       </c>
       <c r="C14" t="n">
-        <v>0.16131856534169</v>
+        <v>0.1613185653416903</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05407003870742388</v>
+        <v>-0.05407003870742472</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5782871175073435</v>
+        <v>0.5782871175073443</v>
       </c>
       <c r="F14" t="n">
-        <v>0.104207646009069</v>
+        <v>0.1042076460090699</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.121769811359689</v>
+        <v>0.1217698113596888</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1773010282590528</v>
+        <v>0.1773010282590537</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2257338184499728</v>
+        <v>-0.2257338184499747</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4692734411693508</v>
+        <v>0.4692734411693524</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4922106710207459</v>
+        <v>0.4922106710207487</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09452849173092565</v>
+        <v>-0.0945284917309256</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1774418821294867</v>
+        <v>0.1774418821294875</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.442308190053721</v>
+        <v>-0.4423081900537226</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2532512065918697</v>
+        <v>0.2532512065918714</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5942209726114963</v>
+        <v>0.5942209726114982</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1837143702306887</v>
+        <v>0.1837143702306886</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1637040102408049</v>
+        <v>0.1637040102408058</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1371395939660652</v>
+        <v>-0.1371395939660669</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5045683344274425</v>
+        <v>0.5045683344274441</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2617625340704764</v>
+        <v>0.2617625340704789</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06981748387247652</v>
+        <v>-0.06981748387247649</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1930840620841167</v>
+        <v>0.1930840620841175</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4482552915460412</v>
+        <v>-0.4482552915460427</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3086203238010881</v>
+        <v>0.3086203238010897</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7176575952681559</v>
+        <v>0.717657595268157</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1969655303245181</v>
+        <v>0.1969655303245182</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1779209025639866</v>
+        <v>0.1779209025639873</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1517530307977557</v>
+        <v>-0.1517530307977571</v>
       </c>
       <c r="E19" t="n">
-        <v>0.545684091446792</v>
+        <v>0.5456840914467934</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2682766969715202</v>
+        <v>0.2682766969715222</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1322032620606822</v>
+        <v>0.1322032620606821</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1728217080449768</v>
+        <v>0.1728217080449772</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2065210614541684</v>
+        <v>-0.2065210614541692</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4709275855755328</v>
+        <v>0.4709275855755335</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4442899600438306</v>
+        <v>0.4442899600438317</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.141198931221375</v>
+        <v>0.1411989312213749</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1536032454395486</v>
+        <v>0.1536032454395495</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1598578977486066</v>
+        <v>-0.1598578977486085</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4422557601913565</v>
+        <v>0.4422557601913583</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3579677249885992</v>
+        <v>0.3579677249886023</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03228862083243213</v>
+        <v>-0.03228862083243202</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1700096908231716</v>
+        <v>0.1700096908231726</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3655014918686382</v>
+        <v>-0.3655014918686401</v>
       </c>
       <c r="E22" t="n">
-        <v>0.300924250203774</v>
+        <v>0.3009242502037761</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8493700668133817</v>
+        <v>0.8493700668133831</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1992,16 +1992,16 @@
         <v>0.2528578615211169</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1707882512439054</v>
+        <v>0.170788251243906</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08188095989951566</v>
+        <v>-0.08188095989951694</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5875966829417496</v>
+        <v>0.5875966829417508</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1387307179459414</v>
+        <v>0.1387307179459428</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1009814874983657</v>
+        <v>0.1009814874983659</v>
       </c>
       <c r="C24" t="n">
         <v>0.1174236802772657</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1291646967772213</v>
+        <v>-0.1291646967772211</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3311276717739527</v>
+        <v>0.331127671773953</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3898025510379953</v>
+        <v>0.3898025510379947</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00433005390115218</v>
+        <v>0.004330053901152394</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08182631997408571</v>
+        <v>0.08182631997408578</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1560465862355063</v>
+        <v>-0.1560465862355062</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1647066940378106</v>
+        <v>0.164706694037811</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9577975473342356</v>
+        <v>0.9577975473342335</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.05122561371632553</v>
+        <v>-0.05122561371632558</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1055959012379953</v>
+        <v>0.1055959012379951</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2581897770578447</v>
+        <v>-0.2581897770578444</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1557385496251937</v>
+        <v>0.1557385496251933</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6275984125035583</v>
+        <v>0.6275984125035574</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1108286684308806</v>
+        <v>-0.1108286684308805</v>
       </c>
       <c r="C27" t="n">
         <v>0.1140937462761546</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3344483019933944</v>
+        <v>-0.3344483019933945</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1127909651316332</v>
+        <v>0.1127909651316334</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3313578400077078</v>
+        <v>0.3313578400077083</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01220396724800446</v>
+        <v>-0.01220396724800431</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1180185229028869</v>
+        <v>0.1180185229028871</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2435160216462784</v>
+        <v>-0.2435160216462785</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2191080871502694</v>
+        <v>0.2191080871502699</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9176397829023973</v>
+        <v>0.9176397829023986</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,16 +2139,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09048136114066323</v>
+        <v>0.09048136114066326</v>
       </c>
       <c r="C29" t="n">
         <v>0.1120837691629425</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1291987896702051</v>
+        <v>-0.1291987896702052</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3101615119515316</v>
+        <v>0.3101615119515317</v>
       </c>
       <c r="F29" t="n">
         <v>0.4195135299990498</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04579550992862588</v>
+        <v>-0.04579550992862566</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0390974269238337</v>
+        <v>0.03909742692383593</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1224250585875266</v>
+        <v>-0.1224250585875307</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03083403873027481</v>
+        <v>0.0308340387302794</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2414710814149033</v>
+        <v>0.2414710814149321</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0009841142683511377</v>
+        <v>-0.01832790500755673</v>
       </c>
       <c r="C31" t="n">
-        <v>0.005676324387152102</v>
+        <v>0.07641092741851577</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01210950563173565</v>
+        <v>-0.1680905707731518</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01014127709503338</v>
+        <v>0.1314347607580383</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8623592324210241</v>
+        <v>0.8104389944348603</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.009996935471112991</v>
+        <v>0.4536514594486488</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006231431833130104</v>
+        <v>0.03633543277518615</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0222103174361644</v>
+        <v>0.3824353198466076</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00221644649393842</v>
+        <v>0.5248675990506899</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1086532664978456</v>
+        <v>9.003178021298596e-36</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.02241147003507639</v>
+        <v>-0.009996935471112977</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01594802218291595</v>
+        <v>0.006231431833130268</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0536690191382375</v>
+        <v>-0.02221031743616471</v>
       </c>
       <c r="E33" t="n">
-        <v>0.008846079068084715</v>
+        <v>0.002216446493938757</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1599374102620117</v>
+        <v>0.1086532664978554</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4536514594486488</v>
+        <v>-0.0009841142683511374</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0363354327751863</v>
+        <v>0.005676324387152115</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3824353198466073</v>
+        <v>-0.01210950563173568</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5248675990506901</v>
+        <v>0.0101412770950334</v>
       </c>
       <c r="F34" t="n">
-        <v>9.003178021304643e-36</v>
+        <v>0.8623592324210245</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.01832790500755672</v>
+        <v>-0.0224114700350764</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07641092741851577</v>
+        <v>0.0159480221829158</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1680905707731518</v>
+        <v>-0.05366901913823723</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1314347607580383</v>
+        <v>0.008846079068084434</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8104389944348604</v>
+        <v>0.1599374102620077</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2314,19 +2314,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.005570573422178937</v>
+        <v>0.00557057342217894</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005006598757322851</v>
+        <v>0.005006598757322847</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.004242179827216841</v>
+        <v>-0.00424217982721683</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01538332667157472</v>
+        <v>0.01538332667157471</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2658603809065231</v>
+        <v>0.2658603809065224</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.680600179802939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981503</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.938181768273511e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,7 +2394,7 @@
         <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
         <v>0.79975540801217</v>
@@ -2410,10 +2410,10 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442914</v>
+        <v>0.2335027157442915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713548</v>
       </c>
     </row>
     <row r="7">
@@ -2458,10 +2458,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2474,10 +2474,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432469</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409136</v>
+        <v>0.1695280942409139</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342821e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.0445652077261707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.260402103171632</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517843</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.326113242387764</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118148</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
         <v>0.7550514391424692</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123743</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307935</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.004000986240379481</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655132</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.677652912256731</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546282</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.02557154094223237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966677</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376411</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541021</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222787</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719854</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.269674845496591</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806365</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.0810583897517186</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074268</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2746,10 +2746,10 @@
         <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103854e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377478</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757815</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400221</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975739</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223567</v>
+        <v>0.1613683918223571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120158</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742094</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290169</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
     <row r="31">
@@ -2839,45 +2839,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.008304876992454899</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.5461741835341518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.002418133412192865</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.007135781003458533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.7347043603418282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.004129656026475429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.02222260881033176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.8525770672961277</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.006335499136474494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.006871422968197173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.3565249957666431</v>
       </c>
     </row>
   </sheetData>
